--- a/reports/drill_1_report.xlsx
+++ b/reports/drill_1_report.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14 08:33:49</t>
+          <t>2026-06-14 09:18:24</t>
         </is>
       </c>
     </row>
@@ -503,7 +503,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14 08:33:50</t>
+          <t>2026-06-14 09:18:24</t>
         </is>
       </c>
     </row>
